--- a/data/file_generation/reference/data_70/各月按部门薪酬发放明细_按部门合并_res.xlsx
+++ b/data/file_generation/reference/data_70/各月按部门薪酬发放明细_按部门合并_res.xlsx
@@ -22829,26 +22829,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFBFD5C9-998C-4169-9625-379E515C9065}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CE81A4E-FA2B-486B-B8BD-8446E8452777}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FD1130C-F9BD-4268-ABAD-261C4E6863B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31E2A571-0CBD-4D46-8B88-2924B8F810B4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F212854-2307-447E-B737-369862EEFA95}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07A52DE0-7098-4847-A7A9-735D19EA92DC}"/>
 </file>